--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67723_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67723_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3cc9aad0f796427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0131dd8cfa7a45dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    491.5230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    476.5038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    545.9676</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    602.2896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    564.7416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    495.2778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    395.7756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    401.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    410.7948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67723_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67723_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0131dd8cfa7a45dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rea180a0e79fb4b85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    596.6574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    444.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    423.9366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    444.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    435.2010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    478.3812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    499.0326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    538.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    649.2246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    823.8228</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    472.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    463.3620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    568.4964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    510.2970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    418.3044</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    433.3236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    491.5230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    457.7298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    446.4654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    497.1552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    572.2512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    679.2630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    714.9336</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    639.8376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    636.0828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    636.0828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    358.2276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    361.9824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    388.2660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    448.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    478.3812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    478.3812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    425.8140</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    384.5112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    377.0016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    382.6338</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    399.5304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    361.9824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    390.1434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    384.5112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    392.0208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    399.5304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    425.8140</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    487.7682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    553.4772</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    713.0562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    504.6648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    504.6648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
